--- a/data/trans_orig/IP05A03-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP05A03-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>81393</t>
+          <t>80605</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>93884</t>
+          <t>93436</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>92150</t>
+          <t>92420</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>105947</t>
+          <t>106148</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>177966</t>
+          <t>177223</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>195999</t>
+          <t>195990</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>9775</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21433</t>
+          <t>21944</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12487</t>
+          <t>12138</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25633</t>
+          <t>25602</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25400</t>
+          <t>25135</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42214</t>
+          <t>42791</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,84%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>702</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6275</t>
+          <t>6612</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11048</t>
+          <t>11081</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>197824</t>
+          <t>196921</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>217052</t>
+          <t>215929</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>195276</t>
+          <t>195392</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>215168</t>
+          <t>215071</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>396779</t>
+          <t>398050</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>425554</t>
+          <t>425585</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,6%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28505</t>
+          <t>29169</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47010</t>
+          <t>47262</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31791</t>
+          <t>31332</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51102</t>
+          <t>50176</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>66325</t>
+          <t>66124</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>93049</t>
+          <t>91912</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3424</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11794</t>
+          <t>11765</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,82 +1430,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>5402</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2648</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9585</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>3,81%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>12039</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>6830</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>18597</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>1,36%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5402</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2674</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9606</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>12039</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>7446</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>19269</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>90469</t>
+          <t>90657</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>105539</t>
+          <t>106167</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>106290</t>
+          <t>105074</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>120667</t>
+          <t>120592</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>201846</t>
+          <t>201187</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>223444</t>
+          <t>223333</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,0%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19708</t>
+          <t>18671</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33884</t>
+          <t>33337</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17595</t>
+          <t>17417</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31845</t>
+          <t>32029</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39188</t>
+          <t>39716</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59817</t>
+          <t>60395</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,45%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7325</t>
+          <t>7280</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8349</t>
+          <t>8097</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3695</t>
+          <t>3686</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13171</t>
+          <t>12251</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>152289</t>
+          <t>152371</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>169338</t>
+          <t>169080</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>164156</t>
+          <t>163396</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>180366</t>
+          <t>180600</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>321541</t>
+          <t>321223</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>345469</t>
+          <t>343808</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,06%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19130</t>
+          <t>19405</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34774</t>
+          <t>35136</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20613</t>
+          <t>19816</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35659</t>
+          <t>35819</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>43735</t>
+          <t>44275</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>65310</t>
+          <t>65479</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,39%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11082</t>
+          <t>10774</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10618</t>
+          <t>10576</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7223</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18510</t>
+          <t>18012</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>537555</t>
+          <t>536907</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>569528</t>
+          <t>570037</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>576466</t>
+          <t>575875</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>609015</t>
+          <t>607924</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1122109</t>
+          <t>1121239</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1169005</t>
+          <t>1168600</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,55%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>91006</t>
+          <t>90003</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>121541</t>
+          <t>121661</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>93234</t>
+          <t>96849</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>124716</t>
+          <t>126016</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>195093</t>
+          <t>193510</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>239113</t>
+          <t>238382</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,04%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12263</t>
+          <t>12340</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26136</t>
+          <t>26411</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12595</t>
+          <t>11982</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26168</t>
+          <t>25957</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27966</t>
+          <t>27496</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>47443</t>
+          <t>47163</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>122242</t>
+          <t>122026</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>134821</t>
+          <t>134607</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>124139</t>
+          <t>123767</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>135493</t>
+          <t>135431</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>250439</t>
+          <t>251489</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>267793</t>
+          <t>267155</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,0%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10794</t>
+          <t>10652</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22691</t>
+          <t>22679</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6599</t>
+          <t>6646</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17369</t>
+          <t>17120</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19240</t>
+          <t>20307</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35928</t>
+          <t>35397</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4491</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>621</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5703</t>
+          <t>5735</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8187</t>
+          <t>7415</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>196947</t>
+          <t>196063</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>213286</t>
+          <t>212747</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>224457</t>
+          <t>223921</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>242688</t>
+          <t>242035</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>425588</t>
+          <t>425122</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>451044</t>
+          <t>451442</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,88%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19624</t>
+          <t>19464</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35071</t>
+          <t>35357</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21131</t>
+          <t>20745</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38273</t>
+          <t>38360</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>45005</t>
+          <t>44940</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>69092</t>
+          <t>69369</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,81%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7592</t>
+          <t>6941</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7822</t>
+          <t>8367</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3586</t>
+          <t>3435</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12567</t>
+          <t>12403</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>132681</t>
+          <t>132394</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>145384</t>
+          <t>144834</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>129285</t>
+          <t>128921</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>142884</t>
+          <t>143290</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>266620</t>
+          <t>266465</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>285844</t>
+          <t>284972</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,77%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9247</t>
+          <t>9455</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21142</t>
+          <t>21449</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13868</t>
+          <t>12961</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27368</t>
+          <t>27036</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25840</t>
+          <t>26194</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44612</t>
+          <t>44126</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,06%</t>
         </is>
       </c>
     </row>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5067</t>
+          <t>4076</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>618</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6567</t>
+          <t>5778</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7746</t>
+          <t>7927</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>141444</t>
+          <t>141566</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>155090</t>
+          <t>155585</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>150914</t>
+          <t>150473</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>164254</t>
+          <t>164293</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>296074</t>
+          <t>296552</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>316721</t>
+          <t>316610</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,49%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10134</t>
+          <t>10206</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22667</t>
+          <t>22674</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13200</t>
+          <t>13594</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26622</t>
+          <t>26760</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26531</t>
+          <t>26407</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44716</t>
+          <t>45325</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2218</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10509</t>
+          <t>9553</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>659</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6362</t>
+          <t>6572</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4136</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13381</t>
+          <t>13329</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>609691</t>
+          <t>606861</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>638790</t>
+          <t>636757</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>644218</t>
+          <t>643260</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>673669</t>
+          <t>674148</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1262228</t>
+          <t>1258883</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1303918</t>
+          <t>1300786</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,31%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>58996</t>
+          <t>60812</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>85624</t>
+          <t>89376</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>64624</t>
+          <t>65627</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>93193</t>
+          <t>93439</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>130620</t>
+          <t>133908</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>171065</t>
+          <t>172665</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>6576</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17527</t>
+          <t>17359</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6175</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17865</t>
+          <t>16861</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15504</t>
+          <t>14909</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30582</t>
+          <t>30407</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>103444</t>
+          <t>103561</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>116532</t>
+          <t>116376</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>101425</t>
+          <t>100994</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>113420</t>
+          <t>113528</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>210019</t>
+          <t>209385</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>227273</t>
+          <t>227321</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,71%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8585</t>
+          <t>8602</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19860</t>
+          <t>19543</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7895</t>
+          <t>7867</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19306</t>
+          <t>19175</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18455</t>
+          <t>18630</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33593</t>
+          <t>33844</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2734</t>
+          <t>2901</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10371</t>
+          <t>10490</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>657</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6244</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4614</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13938</t>
+          <t>14048</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>169848</t>
+          <t>170332</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>185987</t>
+          <t>186489</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>204031</t>
+          <t>204748</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>223209</t>
+          <t>223967</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>381665</t>
+          <t>381938</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>406237</t>
+          <t>406421</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,14%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15838</t>
+          <t>15061</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29678</t>
+          <t>29319</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27640</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45606</t>
+          <t>45155</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>46647</t>
+          <t>46831</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>70081</t>
+          <t>70563</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,13%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4988</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13786</t>
+          <t>13913</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2559</t>
+          <t>2663</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10418</t>
+          <t>10752</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9504</t>
+          <t>9286</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21393</t>
+          <t>20620</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>153868</t>
+          <t>152902</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>169558</t>
+          <t>169204</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>142938</t>
+          <t>144605</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>161115</t>
+          <t>161570</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>303805</t>
+          <t>303701</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>327883</t>
+          <t>327458</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,02%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14607</t>
+          <t>14392</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29575</t>
+          <t>28822</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18422</t>
+          <t>17812</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33579</t>
+          <t>32796</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35501</t>
+          <t>35027</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56311</t>
+          <t>56439</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8720</t>
+          <t>8626</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5768</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>17108</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9626</t>
+          <t>9511</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22266</t>
+          <t>22363</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>129667</t>
+          <t>131217</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>147053</t>
+          <t>148071</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>136795</t>
+          <t>136887</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>152620</t>
+          <t>152309</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>272330</t>
+          <t>271458</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>295807</t>
+          <t>296625</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,42%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17557</t>
+          <t>17564</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32289</t>
+          <t>32374</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15041</t>
+          <t>14729</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29608</t>
+          <t>29017</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>35841</t>
+          <t>35394</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>56363</t>
+          <t>57267</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,68%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>4734</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14738</t>
+          <t>14100</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9140</t>
+          <t>9554</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>7766</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>21030</t>
+          <t>19601</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>577559</t>
+          <t>577506</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>608914</t>
+          <t>606699</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>605382</t>
+          <t>605307</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>636797</t>
+          <t>637545</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1191205</t>
+          <t>1192871</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1237713</t>
+          <t>1236750</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,93%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>66127</t>
+          <t>65808</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>93280</t>
+          <t>93197</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>80379</t>
+          <t>81105</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>110195</t>
+          <t>110458</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>154226</t>
+          <t>155021</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>194852</t>
+          <t>193166</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19955</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>36041</t>
+          <t>36276</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16125</t>
+          <t>16688</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32979</t>
+          <t>31880</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,47 +7857,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
+          <t>4,31%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>50621</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>41328</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>64265</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>3,52%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>4,46%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>50621</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>39247</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>63105</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48243</t>
+          <t>48262</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55209</t>
+          <t>55164</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>47904</t>
+          <t>48222</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56294</t>
+          <t>56643</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>99737</t>
+          <t>98848</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>110017</t>
+          <t>110360</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,77%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1787</t>
+          <t>1684</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7897</t>
+          <t>7427</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>3671</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12086</t>
+          <t>11709</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>6865</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16722</t>
+          <t>17180</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4420</t>
+          <t>4300</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>381</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>4053</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>605</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>138869</t>
+          <t>138911</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>149948</t>
+          <t>149811</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>156507</t>
+          <t>156568</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>169940</t>
+          <t>170455</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>299971</t>
+          <t>297755</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>317408</t>
+          <t>316955</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,52%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4015</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13153</t>
+          <t>13369</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6956</t>
+          <t>7484</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19058</t>
+          <t>19214</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>13793</t>
+          <t>13813</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>28444</t>
+          <t>29814</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1749</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8744</t>
+          <t>9680</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10520</t>
+          <t>11274</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5166</t>
+          <t>5273</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16011</t>
+          <t>17146</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>154548</t>
+          <t>154477</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>166100</t>
+          <t>166248</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>189910</t>
+          <t>190203</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>203573</t>
+          <t>203421</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>349272</t>
+          <t>349786</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>367341</t>
+          <t>367391</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,32%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>4906</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15415</t>
+          <t>15170</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5572</t>
+          <t>6018</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18392</t>
+          <t>17218</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12916</t>
+          <t>12794</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29867</t>
+          <t>28364</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7406</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>806</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8100</t>
+          <t>7708</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11661</t>
+          <t>12290</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>156090</t>
+          <t>155649</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>252473</t>
+          <t>251859</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>275436</t>
+          <t>276535</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>291997</t>
+          <t>292540</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>419548</t>
+          <t>425288</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>537848</t>
+          <t>538815</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,45%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17817</t>
+          <t>18403</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>115899</t>
+          <t>115882</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7762</t>
+          <t>7856</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23378</t>
+          <t>22381</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>30357</t>
+          <t>30667</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>154797</t>
+          <t>143676</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>24,92%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>795</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8495</t>
+          <t>7878</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>1468</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11270</t>
+          <t>11110</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3329</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15138</t>
+          <t>14023</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>509684</t>
+          <t>488058</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>612621</t>
+          <t>612787</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>687322</t>
+          <t>685248</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>713034</t>
+          <t>713032</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1181727</t>
+          <t>1194894</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1315168</t>
+          <t>1316579</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,72%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>37474</t>
+          <t>37386</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>141791</t>
+          <t>169473</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>32099</t>
+          <t>33594</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>55430</t>
+          <t>56782</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>78139</t>
+          <t>78757</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>216185</t>
+          <t>203538</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7394</t>
+          <t>6935</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19097</t>
+          <t>19423</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>7882</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21667</t>
+          <t>22536</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18199</t>
+          <t>18474</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36125</t>
+          <t>36084</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,7 +10404,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
